--- a/data/Databaze_investoru.xlsx
+++ b/data/Databaze_investoru.xlsx
@@ -75,19 +75,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -510,22 +510,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aspire11</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>bez omezení oboru</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>růstová fáze, série B+</t>
+          <t>ARX Equity Partners</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>private equity</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>průmysl, zdraví, spotřebitelé</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>buyout, růstová fáze</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -533,1307 +533,1566 @@
           <t>neuvedeno</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>500 mil. EUR (poslední fond)</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Vinted (24. 6. 2026)</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>100 mil. EUR (cíl fondu)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Medicofit, fizioterapija d.o.o. (Slovinsko) (26. 8. 2026)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>Aspire11</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>bez omezení oboru</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>růstová fáze, série B+</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>500 mil. EUR (poslední fond)</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Vinted (24. 6. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>ATERNUS (Aternus Family Office)</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>family office</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>B2B software, fintech, deep tech, e-commerce</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Jutro Medical (PL) (16. 12. 2025)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>BHM Group</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>soukromý investor</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>zdraví, energetika a klima, deep tech, průmysl</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>buyout</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>1,1 mld. EUR (aktiva celé skupiny)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Rein Medical GmbH (DE) (2. 2. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Credo Ventures</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>bez omezení oboru</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>pre-seed, seed</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>890 tis. EUR – 4,5 mil. EUR</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>75,9 mil. EUR (poslední fond)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Modeinspect (15. 1. 2026)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Czech Founders VC</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>bez omezení oboru</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>pre-seed</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>50 tis. EUR – 350 tis. EUR</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>10 mil. EUR (poslední fond)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Maxfusion (14. 1. 2026)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>DEPO Ventures</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>obrana, průmysl, fintech, energetika a klima, deep tech</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>pre-seed</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>250 tis. EUR – 500 tis. EUR</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>ArcSpace (1. 9. 2026)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Fazole Ventures</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>B2B software, energetika a klima, fintech, mobilita</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>41 tis. EUR – 824 tis. EUR</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Everbot (16. 9. 2025)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Flying Founders</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>B2B software</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>růstová fáze</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>100 tis. EUR – 500 tis. EUR</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Tiny Empires (17. 9. 2025)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Genesis Capital</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>private equity</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>bez omezení oboru</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>růstová fáze, buyout</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>10 mil. EUR – 45 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>286 mil. EUR (poslední fond)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Fyzioterapie s úsměvem (8. 4. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>i&amp;i Bio</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>zdraví, AI</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>pre-seed, seed, série A</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>500 tis. EUR – 2 mil. EUR</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>45 mil. EUR (spravovaná aktiva)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>T-CURX (DE) (17. 12. 2025)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Impulse Ventures</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>soukromý investor</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>B2B software</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>seed, série A</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>od 25 tis. EUR</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>150,8 mil. EUR (vlastní kapitál)</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Dataddo (20. 12. 2023)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Inven Capital</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>korporátní VC</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>energetika a klima</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>série A, série B+, růstová fáze</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2 mil. EUR – 30 mil. EUR</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>500 mil. EUR (spravovaná aktiva)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Andercore (12. 2. 2026)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>J&amp;T Ventures</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>bez omezení oboru</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>pre-seed, seed, série A</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>300 tis. EUR – 3 mil. EUR</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>120 mil. EUR (spravovaná aktiva)</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Definic (dříve Nordics), Košice (12. 6. 2026)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Jet Ventures (fond Jet Venture 1)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Jet Investment (PE + VC fond Jet Venture 1)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>private equity</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>průmysl, energetika a klima, zdraví, spotřebitelé</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>buyout</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10 mil. EUR – 60 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>300 mil. EUR (cíl fondu)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>GigaScan Technologies (Göteborg) (17. 9. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>JIC Ventures</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>průmysl</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>série A, série B+</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>50 mil. EUR (cíl fondu)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>GigaScan Technologies (Göteborg) (17. 9. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>JIC Ventures</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>deep tech, B2B software</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>pre-seed, seed</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>až 1 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>16,3 mil. EUR (poslední fond)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>FaceUp (21. 5. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Jiří Hlavenka</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>anděl</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>pre-seed, seed</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>od 19 tis. EUR</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Elredo (1. 10. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>JSK Investments (Venture Capital Fund I)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>deep tech, B2B software</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>zdraví, AI, deep tech, energetika a klima</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>seed, série A</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>od 300 tis. EUR</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>20 mil. EUR (cíl fondu)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>MintNeuro (Londýn) (10. 10. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>KAYA VC</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>bez omezení oboru</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>pre-seed, seed, série A</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1 mil. EUR – 3 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>75,7 mil. EUR (poslední fond)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Riptides (23. 4. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Lighthouse Ventures</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>B2B software, fintech, AI</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>pre-seed, seed</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>až 1 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>16,3 mil. EUR (poslední fond)</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>FaceUp (21. 5. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>JSK Investments (Venture Capital Fund I)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>200 tis. EUR – 1 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>23 mil. EUR (předchozí fond)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Ranketta (27. 11. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Look AI Ventures (LAIV)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>zdraví, AI, deep tech, energetika a klima</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>seed, série A</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>od 300 tis. EUR</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>pre-seed, seed</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>250 tis. EUR – 1 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>20 mil. EUR (cíl fondu)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>MintNeuro (Londýn) (10. 10. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>KAYA VC</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Sodex Innovations (13. 7. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Lumus Investment</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>andělský syndikát</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>bez omezení oboru</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>pre-seed, seed, série A</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>1 mil. EUR – 3 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>75,7 mil. EUR (poslední fond)</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Riptides (23. 4. 2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Lighthouse Ventures</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>B2B software, fintech, AI</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>pre-seed, seed</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>200 tis. EUR – 1 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>23 mil. EUR (předchozí fond)</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Ranketta (27. 11. 2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Look AI Ventures (LAIV)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>pre-seed, seed</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>250 tis. EUR – 1 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>20 mil. EUR (cíl fondu)</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Sodex Innovations (13. 7. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Lumus Investment</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>andělský syndikát</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>bez omezení oboru</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>pre-seed, seed</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Kardi AI (28. 4. 2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Miton</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>soukromý investor</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>AI, fintech, zdraví, e-commerce, spotřebitelé</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>pre-seed, seed, série A</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>300 tis. EUR – 2 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>450 mil. EUR (hodnota portfolia)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Bandits (21. 11. 2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>N1 (dříve Nation 1 VC)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>AI, zdraví</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>pre-seed, seed</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>89 tis. EUR – 890 tis. EUR</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>53,4 mil. EUR (součet fondů)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Respeecher (28. 5. 2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Pale Fire Capital</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>soukromý investor</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>e-commerce, B2B software, spotřebitelé, průmysl</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>růstová fáze, buyout</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>2 mld. EUR (spravovaná aktiva)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Zwift (30. 4. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Presto Ventures</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>obrana, deep tech, AI</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>seed, série A</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>500 tis. EUR – 5 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>150 mil. EUR (cíl fondu)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nejmenovaný maďarský startup (tréninková data pro drony a roboty) (15. 5. 2025)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>Michael Rostock-Poplar</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>anděl</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>DecisionRules (6. 5. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Miloš Dendis</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>anděl</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>zdraví</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>pre-seed, seed</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>HTG Medical (14. 7. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Miton</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>soukromý investor</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>AI, fintech, zdraví, e-commerce, spotřebitelé</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>pre-seed, seed, série A</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>300 tis. EUR – 2 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>450 mil. EUR (hodnota portfolia)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Bandits (21. 11. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>N1 (dříve Nation 1 VC)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>AI, zdraví</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>pre-seed, seed</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>89 tis. EUR – 890 tis. EUR</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>53,4 mil. EUR (součet fondů)</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Respeecher (28. 5. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Pale Fire Capital</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>soukromý investor</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce, B2B software, spotřebitelé, průmysl</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>růstová fáze, buyout</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2 mld. EUR (spravovaná aktiva)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Zwift (30. 4. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Presto Ventures</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>obrana, deep tech, AI</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>seed, série A</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>500 tis. EUR – 5 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>150 mil. EUR (cíl fondu)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>nejmenovaný maďarský startup (tréninková data pro drony a roboty) (15. 5. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Purple Ventures</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>bez omezení oboru</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>pre-seed, seed</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>250 tis. EUR – 400 tis. EUR</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>28,9 mil. EUR (poslední fond)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Rightcharge (3. 9. 2026)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>PurposeTech</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>zdraví, energetika a klima</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>pre-seed</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>500 tis. EUR – 1 mil. EUR</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>10 mil. EUR (cíl fondu)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>eNOugh, Tingit (a další z celkem 11 investic) (10. 2. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>QQ Capital</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>family office</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>B2B software</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>seed, série A, série B+, růstová fáze</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Navigara (6. 3. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Reflex Capital</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>1 mil. EUR – 2 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>22 mil. EUR (poslední fond)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>FaceUp (19. 5. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Rockaway Ventures</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>e-commerce, spotřebitelé, mobilita, B2B software, obrana, energetika a klima</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>seed, série A</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>500 tis. EUR – 2 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>55 mil. EUR (poslední fond)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Apptronik (13. 2. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>RSJ Investments</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>AI, deep tech, zdraví</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>pre-seed, seed, série A</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Hedepy (25. 1. 2024)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Seed Starter ČS</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>korporátní VC</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>fintech</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>200 tis. EUR – 1 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Definic (dříve Nordics), Košice (12. 6. 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Soulmates Ventures</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>VC fond</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>energetika a klima, mobilita, zdraví</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>seed, série A</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>až 3 mil. EUR</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>50 mil. EUR (poslední fond)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Rightcharge (3. 9. 2026)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>QQ Capital</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>family office</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>B2B software</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>seed, série A, série B+, růstová fáze</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Navigara (6. 3. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Reflex Capital</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>1 mil. EUR – 2 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>22 mil. EUR (poslední fond)</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>FaceUp (19. 5. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Rockaway Ventures</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce, spotřebitelé, mobilita, B2B software, obrana, energetika a klima</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>seed, série A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>500 tis. EUR – 2 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>55 mil. EUR (poslední fond)</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Apptronik (13. 2. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>RSJ Investments</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>AI, deep tech, zdraví</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>pre-seed, seed, série A</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Hedepy (25. 1. 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Seed Starter ČS</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>korporátní VC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>fintech</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>200 tis. EUR – 1 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Definic (dříve Nordics), Košice (12. 6. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Soulmates Ventures</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>energetika a klima, mobilita, zdraví</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>seed, série A</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>až 3 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>50 mil. EUR (poslední fond)</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Rightcharge (3. 9. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>Springtide Ventures</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>korporátní VC</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>B2B software, AI</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>pre-seed, seed, série A, série B+</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>2,6 mil. EUR – 8,6 mil. EUR</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>ThreatMark (7. 1. 2025)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Tachles VC</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>AI, B2B software, deep tech</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>pre-seed, seed</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>20,2 mil. EUR (poslední fond)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Boost.space (9. 10. 2025)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TCF Capital</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>soukromý investor</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>spotřebitelé, e-commerce, průmysl</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>růstová fáze, buyout</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>30 mil. EUR – 50 mil. EUR</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>720 mil. EUR (hodnota portfolia)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Töpfer Babywelt GmbH (DE) (12. 5. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Tensor Ventures</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>deep tech, AI, zdraví</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>seed, série A</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>41,2 mil. EUR (poslední fond)</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>AppFactor (4. 2. 2026)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Tilia Impact Ventures</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>energetika a klima, zdraví</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>300 tis. EUR – 1,2 mil. EUR</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>26 mil. EUR (poslední fond)</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Flox Intelligence (18. 8. 2026)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Y Soft Ventures</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>korporátní VC</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>průmysl, deep tech, B2B software</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>pre-seed, seed</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>neuvedeno</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>RoboTwin (2. 7. 2025)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>ZAKA VC (dříve ZAKA Startups)</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>VC fond</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>zdraví, průmysl, B2B software, AI</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>pre-seed, seed</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>250 tis. EUR – 300 tis. EUR</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>17 mil. EUR (poslední fond)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Promakhos Therapeutics (23. 4. 2025)</t>
         </is>
@@ -1841,197 +2100,228 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId222"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2043,7 +2333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2069,391 +2359,476 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>3TS Capital Partners</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>mimo rozsah vzorku (bez českého týmu / PE)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Aktivní evropský technologický growth investor (TCEE Fund IV, Patronus 05/2026), ale tým sedí ve Vídni, Varšavě, Bukurešti, Budapešti, Bratislavě a USA – bez českého týmu/správce, takže dle v2 bodu 6 mimo vzorek Česko.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>AgriBoom Ventures</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Agritech fond rodinné firmy AGRO CS (60 mil. EUR z vlastních zdrojů, spuštěn 12/2024), ale žádná investice do soukromé firmy není doložena zdrojem tier A/B; jediný zmíněný případ (Plantee) skončil odkupem firmy AGRO CS, ne investicí fondu.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Benson Oak Capital</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>žádná doložená investice za 3 roky</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Pražský buy-out a growth equity investor (AVG, ETA, Bochemie, Click Insurance); poslední doložená investice je Click Insurance (08/2011) a web se neaktualizuje od 2012. Žádná PE investice po 2023-10-22 nedoložena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Czech IP Lab Ventures</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Fond pro transfer technologií IP Lab Ventures Fund I získal závazek EIF ~27 mil. EUR (09/2026), ale zatím není doložena žádná investice fondu do soukromé firmy – I2 nesplněno. Kandidát na pozdější doplnění (watchlist).</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>CZEGG Ventures (podfond STARTEEPO SICAV)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>investuje jen do burzovních akcií nebo realit</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Nejde o VC do startupů: mandát CZEGG (2020) je financovat emise akcií/dluhopisů zavedených rodinných výrobních firem, které musí vstoupit na trh pražské burzy; skupina STARTEEPO se dnes prezentuje jako IPO poradce a hodnotový investor do kotovaných akcií (Warner Bros, Western Digital, Karo Leather). Žádný startupový deal z posledních 36 měsíců jsem nenašel.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Direct PRO Ventures (podfond Direct PRO SICAV)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Podfond Direct PRO Ventures existuje v ARES od 11. 11. 2025, ale nenašel jsem žádnou veřejnou informaci o jeho strategii ani žádnou doloženou investici do startupu. Mateřský fond Direct PRO investuje do prioritních akcií firem skupiny Direct (pojišťovna, auto, Fidoo).</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Double Speed rizikový fond</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>investuje jen do burzovních akcií nebo realit</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Retailový pákový podílový fond, který investuje do globálně diverzifikovaného portfolia akcií velkých (kotovaných) společností s pákou; neinvestuje do soukromých firem ani startupů. Slovo 'rizikový' znamená rizikovost, ne rizikový kapitál.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>EMUN TECH (EMUN investiční společnost)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>neinvestuje přímo do firem</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Multi-family office / investiční společnost s fondy kvalifikovaných investorů; EMUN TECH II Access je fond fondů (investuje do evropských early-stage VC fondů), další fondy jsou PE/private credit/infrastruktura a Global Unicorns (late-stage podíly ve firmách nad 1 mld. USD). Přímé investice do startupů nedoloženy, proto mimo vzorek VC-typů.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Fundlift</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>crowdfunding / platforma, sám neinvestuje</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Fundlift je investiční crowdfundingová platforma skupiny Roklen, přes kterou investují drobní investoři do kampaní firem; sám jako investor nevystupuje.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Garage Angels</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>síť / asociace / poradce, sám neinvestuje</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Brněnský klub 20+ andělských investorů (spolek zapsaný 2024) se společnými, veřejně oznámenými dealy; v únoru 2026 doložené investice do VR Life (seed) a Sendance (tier B, datované). Andělská skupina s doložitelnými dealy = typ angel podle v2 bodu 7.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Genesis Capital</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>mimo rozsah vzorku (PLAN §6)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Private equity skupina (od 1999) s fondy GPEF IV a GPEF V; doložené majoritní investice GAF (03/2024, GPEF IV) a Slevomat (11/2025, GPEF V). Typ pe – samostatné VC rameno 'Genesis Ventures' se v Praze nepodařilo doložit, existoval jen růstový fond GGEF I (lower mid-market), jehož tým se od Genesis odděluje.</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>J&amp;T Family Office</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>neinvestuje přímo do firem</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Family Office od J&amp;T je služba správy rodinného majetku pro klienty privátního bankovnictví J&amp;T Banky; vlastní přímá investice do soukromé firmy nenalezena. Investiční platformou skupiny je J&amp;T ARCH Investments, ne tento subjekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Jan Najvárek</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Jediný otevřený zdroj (Lupa, 2026-02-23) ho jmenuje v seznamu investorů skupiny Garage Angels, bez konkrétní investice. Žádná doložená osobní investice (tier A/B) nenalezena; jeho firemní aktivity (ARTIN, spin-offy) jsou zakladatelské, ne andělské.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Jet Ventures (fond Jet Venture 1)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>duplicita</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>VC rameno brněnské skupiny Jet Investment; fond Jet Venture 1 (cíl 50 mil. EUR) investuje do průmyslových B2B tech startupů; v 08–09/2026 oznámil 4 nové investice (GigaScan, Phantasma Labs, Hermetiq, AppNava), portfolio 11 firem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Karel Obluk</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Veřejně se prezentuje jako anděl (prezident CBAA, člen Garage Angels), ale hlavně investuje jako partner fondu Evolution Equity Partners. Osobní andělské investice sám popisuje jako drobné a příležitostné; žádná jmenovitá osobní investice s datem (tier A/B) nenalezena, natož po 2023-10-22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>KB SmartSolutions</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice za 3 roky</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>CVC dcera Komerční banky investující do fintechů (Roger, Upvest, Lemonero). Poslední doložená minoritní investice je navýšení v Lemoneru (cc.cz 2023-07-03), tedy před 2023-10-22; v 2025 jen odkup zbylých 4 % v už ovládaném Upvestu a prodej podílu v Rogeru.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Limerock Ventures</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>mimo rozsah vzorku (bez českého týmu / PE)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Slovenská (Bratislava) poradenská firma s VC ramenem; tým ani správce nejsou v Česku → mimo vzorek (v2 bod 6). E4 by samo neplatilo, protože firma má vlastní investiční vozidlo (registrovaný správce AIF).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Longevitytech.fund</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>nepodařilo se doložit, že subjekt existuje</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Fond Petra Šrámka je zřejmě aktivní (e15 4/2026: ~40 firem, ~50 mil. USD aktiv), ale nepodařilo se dohledat právnickou osobu v registru (ARES, SEC EDGAR) a jediný doklad investice po 2023-10-22 je agregátor CB Insights.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>mAccelerator.vc</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>mimo rozsah vzorku (bez českého týmu / PE)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>CVC fond polské mBank (2017, 50 mil. EUR) se sídlem a týmem ve Varšavě; Česko je jen cílový trh. Bez českého týmu → mimo vzorek. Navíc web maccelerator.vc je dnes parkovaná stránka hostingu a novější deal (od 2023-10) jsem nenašel, takže by šlo i o E6.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Marperger Group</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>žádná doložená investice za 3 roky</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Subjekt existuje (Marperger s.r.o., Plzeň) a deklaruje PE investice do středních firem ve zvláštních situacích, ale jediná dohledatelná investice je Baden Board (DE) z 09/2019; od 2023-10-22 žádná doložená investice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>NEWTON University Angels</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice za 3 roky</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Univerzitní andělský fond (NUAF) s vlastním vozidlem (osoba rizikového kapitálu) a 5–8 malými investicemi, ale žádná investice není doložena s datem po 2023-10-22. Články z 2024 vyjmenovávají portfolio bez dat investic, takže I2 nelze potvrdit.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Národní rozvojový fond</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>neinvestuje přímo do firem</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>NRF (SICAV ve skupině Národní rozvojové banky, určený pro veřejnou infrastrukturu) za celou existenci nepodpořil jediný projekt a ČNB mu na vlastní žádost odňala povolení s právní mocí 3. 5. 2024. Nemá tedy žádnou doloženou investici (I2) a neinvestoval do soukromých firem (I4); nebyl to ani fond fondů, ani přímý VC investor.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Opifer Investments</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice za 3 roky</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Brněnský early-stage investor/akcelerátor (pre-seed/seed, 10 tis.–1 mil. EUR), ale web je z roku 2018 a žádná investice po 2023-10-22 není doložena; portfolio (Runecast, 3Doid, Geo Applications) je bez dat.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Orbit Capital</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>jen dluhové financování</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Veškerá doložená aktivita od 2023-10-22 je venture debt (Venture Debt Fund II, €107M, 5 úvěrových investic). Growth-equity rameno má poslední doloženou equity investici v roce 2022 (Preply), takže aktivní činnost je jen dluh.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Partners Innovation Fund</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Fond kvalifikovaných investorů skupiny Partners (vznik 1/2026, první closing 7/2026), jehož mandát je investovat do finančních a distribučních společností vlastní skupiny Partners; fintech/insurtech jen okrajově. Není to VC do startupů a žádná investice do externí firmy není doložena.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Pointer</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>nepodařilo se doložit, že subjekt existuje</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Nepodařilo se identifikovat žádnou českou crowdfundingovou / investiční platformu ani investora jménem Pointer; subjekty tohoto jména v ARES jsou IT/inženýrské firmy. Nesplněno I1 (ani I2–I4); E1 nelze doložit, protože platforma nebyla nalezena.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>StartupYard</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice za 3 roky</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Akcelerátor, ale s vlastními investičními vozidly (samostatná s.r.o. pro každý batch, Batch 14 založena 2023-12-07, Batch 15 2024-11-14) a investuje formou konvertibilní zápůjčky za cca 5 % equity, takže E2 neplatí. I2 doloženo jen agregátorem (Personeo.ai, duben 2024) a spuštěním 14. a 15. batche s investicí přes konvertibilku.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>The Seeders</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Syndikát andělských investorů kolem zakladatelů Niceboye (založen 2024) s deklarovaným tiketem 1–10 mil. Kč, ale žádná konkrétní investice do třetí firmy není doložena; 'Projekty' na webu jsou vlastní firmy členů a developerský projekt. Právnická osoba nenalezena (ani I1).</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>UP271</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>žádná doložená investice za 3 roky</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Prague investiční společnost Karla Janečka (navazuje na UP21) s portfoliem ~21 projektů, ale žádná investice UP271 po 2023-10-22 není doložena zdrojem tier A/B; portfolio na webu je bez dat.</t>
         </is>

--- a/data/Databaze_investoru.xlsx
+++ b/data/Databaze_investoru.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investoři" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vyřazení" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jak číst" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vysvětlivky" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vyřazení" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jak číst" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +39,14 @@
     <font>
       <i val="1"/>
       <color rgb="00999999"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="4">
@@ -70,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -93,6 +102,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -167,6 +179,58 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>investor-db</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Název investora. Klik otevře jeho web.
+Příklad: Credo Ventures</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Druh investora, tabulka typů je v listu Vysvětlivky.
+Příklad: VC fond, private equity, anděl</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>V jakých oborech investor investuje (podle toho, co sám deklaruje).
+Příklad: AI, fintech, zdraví; „bez omezení oboru“ = investuje do čehokoli</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>V jakém stadiu vývoje jsou firmy, do kterých investuje — tabulka fází je v listu Vysvětlivky.
+Příklad: pre-seed, seed = velmi mladé firmy</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Kolik obvykle vloží do jedné firmy (tzv. tiket).
+Příklad: 250 tis. – 1 mil. EUR</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Kolik peněz má investor celkem; v závorce co číslo znamená (tabulka v listu Vysvětlivky).
+Příklad: 75,9 mil. EUR (poslední fond)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Poslední veřejně doložená investice za poslední 3 roky. Klik otevře článek nebo tiskovou zprávu.
+Příklad: Modeinspect (15. 1. 2026)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2324,10 +2388,548 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId222"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Vysvětlivky</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Co znamená který sloupec</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Sloupec</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Co znamená</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Příklad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Název investora. Klik otevře jeho web.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Credo Ventures</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Druh investora, tabulka typů je v listu Vysvětlivky.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>VC fond, private equity, anděl</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sektor</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>V jakých oborech investor investuje (podle toho, co sám deklaruje).</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>AI, fintech, zdraví; „bez omezení oboru“ = investuje do čehokoli</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Do čeho investuje (fáze)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>V jakém stadiu vývoje jsou firmy, do kterých investuje — tabulka fází je v listu Vysvětlivky.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>pre-seed, seed = velmi mladé firmy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Typická výše investice</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Kolik obvykle vloží do jedné firmy (tzv. tiket).</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>250 tis. – 1 mil. EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Celkový kapitál</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Kolik peněz má investor celkem; v závorce co číslo znamená (tabulka v listu Vysvětlivky).</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>75,9 mil. EUR (poslední fond)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Doklad, že investuje (firma, datum)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Poslední veřejně doložená investice za poslední 3 roky. Klik otevře článek nebo tiskovou zprávu.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Modeinspect (15. 1. 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Fáze — v jakém stadiu jsou firmy, do kterých investor investuje</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Fáze</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Co to znamená</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Typická investice</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>pre-seed</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>jen nápad nebo první prototyp, často ještě bez firmy</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>desítky až stovky tisíc EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>první produkt, první zákazníci</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>stovky tisíc až ~2 mil. EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>série A</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>produkt funguje, firma roste a potřebuje peníze na škálování</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>jednotky milionů EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>série B+</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>další růstová kola, expanze do zahraničí</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>desítky milionů EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>růstová fáze</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>zavedená firma, investor kupuje menšinový podíl</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>desítky milionů EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>buyout</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>investor kupuje celou firmu nebo většinu (typické pro private equity)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>desítky až stovky mil. EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Celkový kapitál — co znamená údaj v závorce</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>V závorce</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Co číslo znamená</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>poslední fond</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>velikost posledního uzavřeného fondu</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>cíl fondu</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>kolik fond chce vybrat — uzavření zatím není doložené</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>předchozí fond</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>velikost staršího fondu (aktuální není veřejná)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>součet fondů</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>všechny fondy investora dohromady</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>spravovaná aktiva</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>vše, co investor spravuje (AUM), i mimo startupy</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>hodnota portfolia</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>současná hodnota firem, ve kterých má podíl — ne volné peníze</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>vlastní kapitál</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>investor investuje vlastní peníze (bez cizích investorů)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>aktiva celé skupiny</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>majetek celé skupiny vč. nemovitostí — ne jen peníze na investice</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Typy investorů</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Co to je</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>VC fond</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>fond rizikového kapitálu, investuje do startupů</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>private equity</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>kupuje podíly nebo celé zralé firmy</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>korporátní VC</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>investiční rameno firmy nebo banky</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>family office</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>spravuje a investuje majetek jedné rodiny (a tak se sám označuje)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>soukromý investor</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>investiční skupina podnikatele, investuje vlastní peníze</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>anděl</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>fyzická osoba investující vlastní peníze do startupů</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>andělský syndikát</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>skupina andělů investující přes společnou firmu</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>„neuvedeno“ = investor údaj veřejně neuvádí; neodhadujeme ho. Částky v jiných měnách jsou přepočtené na EUR kurzem ECB k datu zdroje.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2839,13 +3441,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2861,33 +3463,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>„neuvedeno“ = investor údaj veřejně neuvádí. Neodhadujeme ho.</t>
+          <t>Co znamená který sloupec, fáze (pre-seed, seed…) a údaje u kapitálu: list „Vysvětlivky“ (nebo najeď myší na záhlaví sloupce).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Částky v jiných měnách přepočteny na EUR kurzem ECB k datu zdroje.</t>
+          <t>„neuvedeno“ = investor údaj veřejně neuvádí. Neodhadujeme ho.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Celkový kapitál: v závorce, co číslo znamená (poslední fond / cíl fondu / spravovaná aktiva…).</t>
+          <t>Částky v jiných měnách přepočteny na EUR kurzem ECB k datu zdroje.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Doklad: poslední veřejně doložená investice za poslední 3 roky; klik otevře článek nebo tiskovou zprávu.</t>
+          <t>Celkový kapitál: v závorce, co číslo znamená (poslední fond / cíl fondu / spravovaná aktiva…).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>Doklad: poslední veřejně doložená investice za poslední 3 roky; klik otevře článek nebo tiskovou zprávu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Pravidla zařazení: PLAN.md. Plné záznamy s citacemi: data/records/.</t>
         </is>

--- a/data/Databaze_investoru.xlsx
+++ b/data/Databaze_investoru.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>růstová fáze</t>
+          <t>růstová fáze, buyout</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1174,9 +1174,9 @@
           <t>anděl</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>neuvedeno</t>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>B2B software, AI</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2250,142 +2250,143 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId223"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
